--- a/docs/周绩效考核表-研发中心陈芋如20260621.xlsx
+++ b/docs/周绩效考核表-研发中心陈芋如20260621.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkBuddy\Daily\模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Digital-transformation\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88639E31-B71F-40E0-ADD8-D1C04EA912B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD516437-0D88-4DB0-8A99-B3580E94E66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -294,21 +294,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -324,42 +317,52 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -644,429 +647,396 @@
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.75" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24.75" style="25" customWidth="1"/>
-    <col min="4" max="4" width="25.375" style="25" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" customWidth="1"/>
-    <col min="8" max="8" width="26.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10" style="6"/>
+    <col min="8" max="8" width="26.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4" spans="1:8" s="16" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="11"/>
+    </row>
+    <row r="4" spans="1:8" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="11"/>
+      <c r="H4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="18">
+      <c r="D5" s="11"/>
+      <c r="E5" s="9">
         <v>46188</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="18">
+      <c r="G5" s="11"/>
+      <c r="H5" s="9">
         <v>46188</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19"/>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="18">
+      <c r="D6" s="26"/>
+      <c r="E6" s="9">
         <v>46188</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="18">
+      <c r="G6" s="11"/>
+      <c r="H6" s="9">
         <v>46188</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19"/>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="18">
+      <c r="D7" s="11"/>
+      <c r="E7" s="9">
         <v>46189</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="18">
+      <c r="G7" s="11"/>
+      <c r="H7" s="9">
         <v>46189</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="18">
+      <c r="D8" s="11"/>
+      <c r="E8" s="9">
         <v>46190</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="18">
+      <c r="G8" s="11"/>
+      <c r="H8" s="9">
         <v>46190</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="18">
+      <c r="D9" s="11"/>
+      <c r="E9" s="9">
         <v>46191</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="18">
+      <c r="G9" s="11"/>
+      <c r="H9" s="9">
         <v>46190</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="18" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="18">
+      <c r="G10" s="11"/>
+      <c r="H10" s="9">
         <v>46191</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="18" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="18">
+      <c r="G11" s="11"/>
+      <c r="H11" s="9">
         <v>46194</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="18"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="18"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="18"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="18"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="18">
+      <c r="D16" s="11"/>
+      <c r="E16" s="9">
         <v>46195</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="18"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="8" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="18">
+      <c r="D17" s="11"/>
+      <c r="E17" s="9">
         <v>46196</v>
       </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="18"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19"/>
-      <c r="B18" s="8" t="s">
+      <c r="A18" s="18"/>
+      <c r="B18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="18">
+      <c r="D18" s="11"/>
+      <c r="E18" s="9">
         <v>46197</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="18"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19"/>
-      <c r="B19" s="8" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="18">
+      <c r="D19" s="11"/>
+      <c r="E19" s="9">
         <v>46198</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="18"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19"/>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="18"/>
+      <c r="B20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="18">
+      <c r="D20" s="11"/>
+      <c r="E20" s="9">
         <v>46199</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="18"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="18"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="8"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:8" s="16" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="24" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" s="8" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A16:A23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="A1:H1"/>
@@ -1079,6 +1049,39 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A16:A23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
